--- a/data/trans_orig/P19C07-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C07-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8469</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9740</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14196</t>
+          <t>13883</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>183024</t>
+          <t>183012</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>190542</t>
+          <t>190550</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>191482</t>
+          <t>191577</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>200233</t>
+          <t>200232</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>378520</t>
+          <t>378833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>388995</t>
+          <t>389161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>21291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>11305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28802</t>
+          <t>28638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21820</t>
+          <t>21988</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43330</t>
+          <t>43157</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>388723</t>
+          <t>388465</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403596</t>
+          <t>403393</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>412399</t>
+          <t>412563</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>429746</t>
+          <t>429896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>807627</t>
+          <t>807800</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>829137</t>
+          <t>828969</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9181</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17520</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>227356</t>
+          <t>227017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>235519</t>
+          <t>235534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>277054</t>
+          <t>277126</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>286854</t>
+          <t>286843</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>507823</t>
+          <t>507682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>520462</t>
+          <t>520434</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15563</t>
+          <t>15985</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>11509</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28646</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>17611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37855</t>
+          <t>37851</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>251968</t>
+          <t>251546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>263825</t>
+          <t>263738</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>270888</t>
+          <t>270471</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>288107</t>
+          <t>288025</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>529210</t>
+          <t>529214</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>549328</t>
+          <t>549454</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14867</t>
+          <t>15469</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>15047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22729</t>
+          <t>23433</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>155411</t>
+          <t>154809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166645</t>
+          <t>166423</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160501</t>
+          <t>158859</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171738</t>
+          <t>171214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>321455</t>
+          <t>320751</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>335786</t>
+          <t>335734</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11804</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182740</t>
+          <t>182648</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>195451</t>
+          <t>195615</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>203466</t>
+          <t>203470</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>381954</t>
+          <t>381991</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>391783</t>
+          <t>391786</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25619</t>
+          <t>27087</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25335</t>
+          <t>25254</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22775</t>
+          <t>22575</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45102</t>
+          <t>45451</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>438706</t>
+          <t>437238</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>454169</t>
+          <t>454275</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>514033</t>
+          <t>514114</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>530379</t>
+          <t>530361</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>958590</t>
+          <t>958241</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>980917</t>
+          <t>981117</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>20376</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40194</t>
+          <t>42535</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32706</t>
+          <t>32877</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38409</t>
+          <t>38500</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66871</t>
+          <t>67230</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>485358</t>
+          <t>483017</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>506042</t>
+          <t>505176</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>559706</t>
+          <t>559535</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>578570</t>
+          <t>577966</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1051092</t>
+          <t>1050733</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1079554</t>
+          <t>1079463</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>66285</t>
+          <t>66970</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>103953</t>
+          <t>104631</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>77527</t>
+          <t>77052</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>117081</t>
+          <t>115636</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>156069</t>
+          <t>154068</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>208510</t>
+          <t>205090</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2350789</t>
+          <t>2350111</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2388457</t>
+          <t>2387772</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2623856</t>
+          <t>2625301</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2663410</t>
+          <t>2663885</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4987169</t>
+          <t>4990589</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5039610</t>
+          <t>5041611</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2012 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18549</t>
+          <t>18161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21246</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13282</t>
+          <t>13705</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33285</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232011</t>
+          <t>232399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246617</t>
+          <t>246551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>227993</t>
+          <t>228603</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>243298</t>
+          <t>243182</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>466515</t>
+          <t>466678</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>486518</t>
+          <t>486095</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27234</t>
+          <t>27680</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>19816</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>19942</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41244</t>
+          <t>40844</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>379096</t>
+          <t>378650</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>395439</t>
+          <t>395124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>418130</t>
+          <t>418007</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432572</t>
+          <t>431812</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>802909</t>
+          <t>803309</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>825388</t>
+          <t>824211</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>14318</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21667</t>
+          <t>20807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13572</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31890</t>
+          <t>29617</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>280060</t>
+          <t>279346</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>290139</t>
+          <t>289889</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307085</t>
+          <t>307945</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321770</t>
+          <t>321925</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>590526</t>
+          <t>592799</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>608844</t>
+          <t>609537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19652</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26142</t>
+          <t>23488</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15054</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36360</t>
+          <t>37333</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293425</t>
+          <t>294487</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>308384</t>
+          <t>309029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>316673</t>
+          <t>319327</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>334139</t>
+          <t>334044</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>619531</t>
+          <t>618558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>640837</t>
+          <t>640184</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11913</t>
+          <t>11556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18499</t>
+          <t>19662</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180878</t>
+          <t>180847</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190069</t>
+          <t>190113</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182669</t>
+          <t>183026</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192594</t>
+          <t>192606</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>368141</t>
+          <t>366978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>380733</t>
+          <t>380716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13373</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21089</t>
+          <t>20962</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30693</t>
+          <t>30625</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236600</t>
+          <t>236262</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247086</t>
+          <t>247109</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243741</t>
+          <t>243868</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>258513</t>
+          <t>258201</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>484110</t>
+          <t>484178</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>503263</t>
+          <t>503157</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34572</t>
+          <t>33858</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9932</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27054</t>
+          <t>26436</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27097</t>
+          <t>26825</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53585</t>
+          <t>53685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>540519</t>
+          <t>541233</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>562408</t>
+          <t>561761</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>598933</t>
+          <t>599551</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>616055</t>
+          <t>615451</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1147493</t>
+          <t>1147393</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1173981</t>
+          <t>1174253</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29549</t>
+          <t>29364</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>17909</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39881</t>
+          <t>39540</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33861</t>
+          <t>34602</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61244</t>
+          <t>62632</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>604356</t>
+          <t>604541</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>621816</t>
+          <t>621764</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>662413</t>
+          <t>662754</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>684425</t>
+          <t>684385</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1274955</t>
+          <t>1273567</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1302338</t>
+          <t>1301597</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>78057</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>117722</t>
+          <t>118212</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>92956</t>
+          <t>92424</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>137195</t>
+          <t>134191</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>183513</t>
+          <t>180317</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>240628</t>
+          <t>240083</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2796937</t>
+          <t>2796447</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2836602</t>
+          <t>2835812</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3009126</t>
+          <t>3012130</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3053365</t>
+          <t>3053897</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5820352</t>
+          <t>5820897</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5877467</t>
+          <t>5880663</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>21490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>13028</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29414</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22388</t>
+          <t>22730</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>44735</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223891</t>
+          <t>223728</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238030</t>
+          <t>238244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216920</t>
+          <t>216494</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>234249</t>
+          <t>233306</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>448388</t>
+          <t>446816</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>469163</t>
+          <t>468821</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14995</t>
+          <t>15096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17728</t>
+          <t>18343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11619</t>
+          <t>10986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27076</t>
+          <t>27606</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>348170</t>
+          <t>348069</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>360112</t>
+          <t>359259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>375599</t>
+          <t>374984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>388290</t>
+          <t>388028</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729416</t>
+          <t>728886</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>744873</t>
+          <t>745506</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>15988</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18279</t>
+          <t>18290</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28924</t>
+          <t>29881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274597</t>
+          <t>274519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>286684</t>
+          <t>286088</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>289485</t>
+          <t>289474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302918</t>
+          <t>302991</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>569346</t>
+          <t>568389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>586338</t>
+          <t>586730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16421</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29444</t>
+          <t>27869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>313626</t>
+          <t>313481</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>326362</t>
+          <t>326918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>331997</t>
+          <t>332591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>344068</t>
+          <t>344058</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>649464</t>
+          <t>651039</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>667614</t>
+          <t>668865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>13063</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18719</t>
+          <t>18803</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107173</t>
+          <t>106159</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116924</t>
+          <t>116406</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134813</t>
+          <t>134769</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143684</t>
+          <t>143716</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>246003</t>
+          <t>245919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>258426</t>
+          <t>258994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23514</t>
+          <t>23897</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11276</t>
+          <t>11515</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26533</t>
+          <t>27403</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224162</t>
+          <t>224060</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232689</t>
+          <t>232650</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223623</t>
+          <t>223240</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>238621</t>
+          <t>238556</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>454220</t>
+          <t>453350</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>469477</t>
+          <t>469238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14030</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>21438</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10554</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27810</t>
+          <t>27758</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>428277</t>
+          <t>429197</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>440115</t>
+          <t>440151</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>466181</t>
+          <t>465613</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>481582</t>
+          <t>481258</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>901548</t>
+          <t>901600</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>918804</t>
+          <t>919709</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14036</t>
+          <t>13239</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32563</t>
+          <t>31908</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14984</t>
+          <t>14878</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34433</t>
+          <t>34570</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32694</t>
+          <t>33125</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59168</t>
+          <t>60157</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>607689</t>
+          <t>608344</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>626216</t>
+          <t>627013</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>656908</t>
+          <t>656771</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>676357</t>
+          <t>676463</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1272425</t>
+          <t>1271436</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1298899</t>
+          <t>1298468</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>59575</t>
+          <t>57493</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>96885</t>
+          <t>93752</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>84044</t>
+          <t>84665</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>123999</t>
+          <t>123209</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>153420</t>
+          <t>152832</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>205803</t>
+          <t>211060</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2567448</t>
+          <t>2570581</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2604758</t>
+          <t>2606840</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2743316</t>
+          <t>2744106</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2783271</t>
+          <t>2782650</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5325845</t>
+          <t>5320588</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5378228</t>
+          <t>5378816</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>9841</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43562</t>
+          <t>46703</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12018</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30626</t>
+          <t>30330</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27164</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66026</t>
+          <t>64491</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261868</t>
+          <t>258727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>296851</t>
+          <t>295589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>256981</t>
+          <t>257277</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275589</t>
+          <t>275701</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>527011</t>
+          <t>528546</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>565873</t>
+          <t>566409</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>10435</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31044</t>
+          <t>29919</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19254</t>
+          <t>19462</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39203</t>
+          <t>39620</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33220</t>
+          <t>32885</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60442</t>
+          <t>61199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>475940</t>
+          <t>477065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496067</t>
+          <t>496549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>462345</t>
+          <t>461928</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>482294</t>
+          <t>482086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>948090</t>
+          <t>947333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>975312</t>
+          <t>975647</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>13674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20359</t>
+          <t>19552</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>286651</t>
+          <t>287518</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>298615</t>
+          <t>298687</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323837</t>
+          <t>324176</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332275</t>
+          <t>332454</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616108</t>
+          <t>616915</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>630053</t>
+          <t>629815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23457</t>
+          <t>18428</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14485</t>
+          <t>14470</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25406</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>286663</t>
+          <t>291692</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>308942</t>
+          <t>309031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>458980</t>
+          <t>458995</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470778</t>
+          <t>470894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>758179</t>
+          <t>756965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>778264</t>
+          <t>777294</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13613</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17325</t>
+          <t>17579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158717</t>
+          <t>158313</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166542</t>
+          <t>166581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188679</t>
+          <t>189783</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199350</t>
+          <t>199287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>353396</t>
+          <t>353142</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>364844</t>
+          <t>364271</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11817</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16763</t>
+          <t>16472</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>241915</t>
+          <t>241685</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252247</t>
+          <t>252243</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>238843</t>
+          <t>239376</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245120</t>
+          <t>245105</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>483319</t>
+          <t>483610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>496309</t>
+          <t>496129</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>13239</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32593</t>
+          <t>33182</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14383</t>
+          <t>17118</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55514</t>
+          <t>55128</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35225</t>
+          <t>33764</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79539</t>
+          <t>77318</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>567102</t>
+          <t>566513</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>586544</t>
+          <t>586456</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>772851</t>
+          <t>773237</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>813982</t>
+          <t>811247</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1348521</t>
+          <t>1350742</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1392835</t>
+          <t>1394296</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42442</t>
+          <t>42287</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23304</t>
+          <t>24022</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45667</t>
+          <t>45519</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34251</t>
+          <t>36971</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78707</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>866197</t>
+          <t>866352</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>897662</t>
+          <t>898444</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>658257</t>
+          <t>658405</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>680620</t>
+          <t>679902</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1533856</t>
+          <t>1534790</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1578312</t>
+          <t>1575592</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>80315</t>
+          <t>78717</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>140899</t>
+          <t>138984</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>112051</t>
+          <t>109933</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>168116</t>
+          <t>165198</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>202167</t>
+          <t>205341</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>290346</t>
+          <t>288038</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3213322</t>
+          <t>3215237</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3273906</t>
+          <t>3275504</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3410711</t>
+          <t>3413629</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3466776</t>
+          <t>3468894</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6642702</t>
+          <t>6645010</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6730881</t>
+          <t>6727707</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C07-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C07-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>988</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9645</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>183012</t>
+          <t>182966</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>190550</t>
+          <t>190554</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>191577</t>
+          <t>191999</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>200232</t>
+          <t>200234</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>378833</t>
+          <t>377478</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>389161</t>
+          <t>388885</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>21365</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28638</t>
+          <t>28817</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21988</t>
+          <t>21251</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43157</t>
+          <t>45809</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>388465</t>
+          <t>388391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403393</t>
+          <t>402937</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>412563</t>
+          <t>412384</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>429896</t>
+          <t>429525</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>807800</t>
+          <t>805148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>828969</t>
+          <t>829706</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9520</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>227017</t>
+          <t>226478</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>277126</t>
+          <t>277005</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>286843</t>
+          <t>286849</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>507682</t>
+          <t>508672</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>520434</t>
+          <t>520433</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15985</t>
+          <t>15596</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11509</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>27498</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>17958</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37851</t>
+          <t>38238</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>251546</t>
+          <t>251935</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>263738</t>
+          <t>263872</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>270471</t>
+          <t>272036</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>288025</t>
+          <t>288359</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>529214</t>
+          <t>528827</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>549454</t>
+          <t>549107</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15469</t>
+          <t>15317</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23433</t>
+          <t>24103</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154809</t>
+          <t>154961</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166423</t>
+          <t>165912</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158859</t>
+          <t>159968</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171214</t>
+          <t>171804</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>320751</t>
+          <t>320081</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>335734</t>
+          <t>335553</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8873</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11767</t>
+          <t>12404</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182648</t>
+          <t>182033</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>195615</t>
+          <t>194829</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>381991</t>
+          <t>381354</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>391786</t>
+          <t>391684</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27087</t>
+          <t>26985</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25254</t>
+          <t>24954</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>22572</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45451</t>
+          <t>45918</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>437238</t>
+          <t>437340</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>454275</t>
+          <t>453742</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>514114</t>
+          <t>514414</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>530361</t>
+          <t>530845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>958241</t>
+          <t>957774</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>981117</t>
+          <t>981120</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20376</t>
+          <t>19581</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42535</t>
+          <t>39794</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>13821</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32877</t>
+          <t>33225</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38500</t>
+          <t>37402</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67230</t>
+          <t>66900</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>483017</t>
+          <t>485758</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>505176</t>
+          <t>505971</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>559535</t>
+          <t>559187</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>577966</t>
+          <t>578591</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1050733</t>
+          <t>1051063</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1079463</t>
+          <t>1080561</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>66970</t>
+          <t>67347</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>104631</t>
+          <t>103332</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>77052</t>
+          <t>78134</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>115636</t>
+          <t>115038</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>154068</t>
+          <t>152983</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>205090</t>
+          <t>207455</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2350111</t>
+          <t>2351410</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2387772</t>
+          <t>2387395</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2625301</t>
+          <t>2625899</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2663885</t>
+          <t>2662803</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4990589</t>
+          <t>4988224</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5041611</t>
+          <t>5042696</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18161</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20636</t>
+          <t>19975</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33122</t>
+          <t>32633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232399</t>
+          <t>232855</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246551</t>
+          <t>246443</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228603</t>
+          <t>229264</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>243182</t>
+          <t>243703</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>466678</t>
+          <t>467167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>486095</t>
+          <t>487071</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27680</t>
+          <t>28076</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19816</t>
+          <t>19718</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>18783</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40844</t>
+          <t>41507</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>378650</t>
+          <t>378254</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>395124</t>
+          <t>395253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>418007</t>
+          <t>418105</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>431812</t>
+          <t>432048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>803309</t>
+          <t>802646</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>824211</t>
+          <t>825370</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20807</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12879</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29617</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>289889</t>
+          <t>289930</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307945</t>
+          <t>307329</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321925</t>
+          <t>321875</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>592799</t>
+          <t>592476</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>609537</t>
+          <t>609316</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18590</t>
+          <t>18848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23488</t>
+          <t>24298</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>15494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37333</t>
+          <t>36485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>294487</t>
+          <t>294229</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309029</t>
+          <t>308916</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>319327</t>
+          <t>318517</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>334044</t>
+          <t>334480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>618558</t>
+          <t>619406</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>640184</t>
+          <t>640397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19662</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180847</t>
+          <t>181712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190113</t>
+          <t>190149</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183026</t>
+          <t>182897</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192606</t>
+          <t>192582</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366978</t>
+          <t>367163</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>380716</t>
+          <t>380861</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>13017</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20962</t>
+          <t>22151</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11646</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30625</t>
+          <t>31093</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236262</t>
+          <t>236956</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247109</t>
+          <t>247128</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243868</t>
+          <t>242679</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>258201</t>
+          <t>258290</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>484178</t>
+          <t>483710</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>503157</t>
+          <t>503078</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13330</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33858</t>
+          <t>33733</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26436</t>
+          <t>25442</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26825</t>
+          <t>27403</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53685</t>
+          <t>52486</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>541233</t>
+          <t>541358</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>561761</t>
+          <t>561297</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>599551</t>
+          <t>600545</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>615451</t>
+          <t>615924</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1147393</t>
+          <t>1148592</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1174253</t>
+          <t>1173675</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>12344</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29364</t>
+          <t>30267</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39540</t>
+          <t>39422</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34602</t>
+          <t>34204</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62632</t>
+          <t>62210</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>604541</t>
+          <t>603638</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>621764</t>
+          <t>621561</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>662754</t>
+          <t>662872</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>684385</t>
+          <t>683831</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1273567</t>
+          <t>1273989</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1301597</t>
+          <t>1301995</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>78847</t>
+          <t>79376</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>118212</t>
+          <t>119741</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>92424</t>
+          <t>93902</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>134191</t>
+          <t>138327</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>180317</t>
+          <t>181344</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>240083</t>
+          <t>239580</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2796447</t>
+          <t>2794918</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2835812</t>
+          <t>2835283</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3012130</t>
+          <t>3007994</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3053897</t>
+          <t>3052419</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5820897</t>
+          <t>5821400</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5880663</t>
+          <t>5879636</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21490</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13028</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>28881</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>23600</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44735</t>
+          <t>43906</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223728</t>
+          <t>224160</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238244</t>
+          <t>238568</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216494</t>
+          <t>217453</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>233306</t>
+          <t>234405</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>446816</t>
+          <t>447645</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>468821</t>
+          <t>467951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15096</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>18450</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>11300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27606</t>
+          <t>29177</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>348069</t>
+          <t>349029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>359259</t>
+          <t>360014</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>374984</t>
+          <t>374877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>388028</t>
+          <t>388298</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>728886</t>
+          <t>727315</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745506</t>
+          <t>745192</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15988</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18290</t>
+          <t>17854</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29881</t>
+          <t>29620</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274519</t>
+          <t>273606</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>286088</t>
+          <t>286625</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>289474</t>
+          <t>289910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302991</t>
+          <t>302874</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>568389</t>
+          <t>568650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>586730</t>
+          <t>586227</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>17275</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>10702</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27869</t>
+          <t>28458</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>313481</t>
+          <t>312772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>326918</t>
+          <t>326266</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>332591</t>
+          <t>331617</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>344058</t>
+          <t>344021</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>651039</t>
+          <t>650450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>668865</t>
+          <t>668206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>12344</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>11626</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18803</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106159</t>
+          <t>106878</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116406</t>
+          <t>116412</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134769</t>
+          <t>133874</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143716</t>
+          <t>143699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>245919</t>
+          <t>245227</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>258994</t>
+          <t>258344</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9555</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23897</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27403</t>
+          <t>26668</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224060</t>
+          <t>224318</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232650</t>
+          <t>232656</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223240</t>
+          <t>224487</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>238556</t>
+          <t>238535</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>453350</t>
+          <t>454085</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>469238</t>
+          <t>469464</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21438</t>
+          <t>20773</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27758</t>
+          <t>28658</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>429197</t>
+          <t>429312</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>440151</t>
+          <t>440131</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>465613</t>
+          <t>466278</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>481258</t>
+          <t>480873</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>901600</t>
+          <t>900700</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>919709</t>
+          <t>918544</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13239</t>
+          <t>13594</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31908</t>
+          <t>31493</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14878</t>
+          <t>14152</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34570</t>
+          <t>32518</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33125</t>
+          <t>31607</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60157</t>
+          <t>58859</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>608344</t>
+          <t>608759</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>627013</t>
+          <t>626658</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>656771</t>
+          <t>658823</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>676463</t>
+          <t>677189</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1271436</t>
+          <t>1272734</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1298468</t>
+          <t>1299986</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>57493</t>
+          <t>60136</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>93752</t>
+          <t>94876</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>84665</t>
+          <t>82376</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>123209</t>
+          <t>121465</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>152832</t>
+          <t>153503</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>211060</t>
+          <t>208873</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2570581</t>
+          <t>2569457</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2606840</t>
+          <t>2604197</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2744106</t>
+          <t>2745850</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2782650</t>
+          <t>2784939</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5320588</t>
+          <t>5322775</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5378816</t>
+          <t>5378145</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21354</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46703</t>
+          <t>29302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19605</t>
+          <t>18812</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30330</t>
+          <t>29268</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>40959</t>
+          <t>34656</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26628</t>
+          <t>23386</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64491</t>
+          <t>49892</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>284076</t>
+          <t>285072</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258727</t>
+          <t>271615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295589</t>
+          <t>292654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>268002</t>
+          <t>290652</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>257277</t>
+          <t>280196</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275701</t>
+          <t>297328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>552078</t>
+          <t>575725</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>528546</t>
+          <t>560489</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>566409</t>
+          <t>586995</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17747</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29919</t>
+          <t>29632</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,27 +11075,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27756</t>
+          <t>29151</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19462</t>
+          <t>20413</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39620</t>
+          <t>41981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -11110,17 +11110,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>45503</t>
+          <t>47353</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32885</t>
+          <t>33804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61199</t>
+          <t>64238</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>489237</t>
+          <t>499826</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>477065</t>
+          <t>488396</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496549</t>
+          <t>507948</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,22 +11188,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>473792</t>
+          <t>502461</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>461928</t>
+          <t>489631</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>482086</t>
+          <t>511199</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,17 +11223,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>963029</t>
+          <t>1002287</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>947333</t>
+          <t>985402</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>975647</t>
+          <t>1015836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13674</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6652</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19552</t>
+          <t>20130</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>294850</t>
+          <t>294099</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>287518</t>
+          <t>286742</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>298687</t>
+          <t>298013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>329391</t>
+          <t>335862</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>324176</t>
+          <t>330804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332454</t>
+          <t>338995</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>624241</t>
+          <t>629960</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616915</t>
+          <t>621805</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>629815</t>
+          <t>635285</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18428</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>17273</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>31166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>304731</t>
+          <t>364766</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>291692</t>
+          <t>348247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309031</t>
+          <t>369591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>466935</t>
+          <t>411114</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>458995</t>
+          <t>402340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470894</t>
+          <t>415681</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>771666</t>
+          <t>775880</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>756965</t>
+          <t>759185</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>777294</t>
+          <t>783285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10116</t>
+          <t>11165</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>13899</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>11652</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17579</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>163572</t>
+          <t>184142</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158313</t>
+          <t>178134</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166581</t>
+          <t>187127</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>196446</t>
+          <t>213308</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>189783</t>
+          <t>205903</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199287</t>
+          <t>216737</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>360019</t>
+          <t>397449</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>353142</t>
+          <t>389656</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>364271</t>
+          <t>402639</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>12003</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16472</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>249037</t>
+          <t>245213</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>241685</t>
+          <t>237732</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252243</t>
+          <t>248006</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>243120</t>
+          <t>248287</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>239376</t>
+          <t>244288</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245105</t>
+          <t>250236</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>492156</t>
+          <t>493499</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>483610</t>
+          <t>486546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>496129</t>
+          <t>497240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21073</t>
+          <t>30552</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13239</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33182</t>
+          <t>47103</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>36136</t>
+          <t>42376</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>31156</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55128</t>
+          <t>59036</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>57208</t>
+          <t>72928</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33764</t>
+          <t>55664</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77318</t>
+          <t>93909</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>578622</t>
+          <t>667128</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>566513</t>
+          <t>650577</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>586456</t>
+          <t>679228</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>792229</t>
+          <t>699010</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>773237</t>
+          <t>682350</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>811247</t>
+          <t>710230</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1370852</t>
+          <t>1366138</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1350742</t>
+          <t>1345157</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1394296</t>
+          <t>1383402</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1428060</t>
+          <t>1439066</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1428060</t>
+          <t>1439066</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1428060</t>
+          <t>1439066</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,67 +13098,67 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>26064</t>
+          <t>31432</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>20762</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42287</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>37663</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>26496</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>51321</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>4,65%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>33371</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>24022</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>45519</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>59436</t>
+          <t>69095</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36971</t>
+          <t>53263</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>77773</t>
+          <t>86381</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -13211,67 +13211,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>882575</t>
+          <t>739618</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>866352</t>
+          <t>725930</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>898444</t>
+          <t>750288</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>94,15%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>772644</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>758986</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>783811</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
           <t>95,35%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>98,88%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>670553</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>658405</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>679902</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1553127</t>
+          <t>1512262</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1534790</t>
+          <t>1494976</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1575592</t>
+          <t>1528094</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>107520</t>
+          <t>117815</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>78717</t>
+          <t>93329</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>138984</t>
+          <t>147596</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>138358</t>
+          <t>152111</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>109933</t>
+          <t>127565</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>165198</t>
+          <t>176936</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>245878</t>
+          <t>269926</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>205341</t>
+          <t>235502</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>288038</t>
+          <t>308107</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3246701</t>
+          <t>3279863</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3215237</t>
+          <t>3250082</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3275504</t>
+          <t>3304349</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3440469</t>
+          <t>3473337</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3413629</t>
+          <t>3448512</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3468894</t>
+          <t>3497883</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6687170</t>
+          <t>6753199</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6645010</t>
+          <t>6715018</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6727707</t>
+          <t>6787623</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
